--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEBRASKA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEBRASKA_2019.xlsx
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C107">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C176">
